--- a/Models/RNWH.xlsx
+++ b/Models/RNWH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36a87f973740ffce/Documents/Personal/Finance/Models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2694" documentId="8_{ED267F20-D94D-D94E-943C-F0483419986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C1AD9B-0AB0-2547-9A30-F7B3AF390C7D}"/>
+  <xr:revisionPtr revIDLastSave="2724" documentId="8_{ED267F20-D94D-D94E-943C-F0483419986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C5F2268-0055-B943-BFCE-6646B89370F4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="30220" windowHeight="17860" activeTab="6" xr2:uid="{2D24E3F0-5AC2-084A-A5AB-A55EC1353B84}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="30220" windowHeight="17860" activeTab="3" xr2:uid="{2D24E3F0-5AC2-084A-A5AB-A55EC1353B84}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="3" r:id="rId1"/>
@@ -2530,7 +2530,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="179" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -3245,7 +3245,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3356,6 +3356,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3371,9 +3383,6 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3387,31 +3396,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="18" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6878,7 +6862,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-UA"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -14289,10 +14273,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -15060,14 +15040,14 @@
       <c r="F1" s="33"/>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
-      <c r="I1" s="86" t="s">
+      <c r="I1" s="96" t="s">
         <v>238</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="88"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="98"/>
     </row>
     <row r="2" spans="1:16">
       <c r="B2" s="20"/>
@@ -16614,18 +16594,18 @@
       <c r="K27" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="M27" s="89" t="s">
+      <c r="M27" s="99" t="s">
         <v>446</v>
       </c>
-      <c r="N27" s="90"/>
-      <c r="P27" s="89" t="s">
+      <c r="N27" s="100"/>
+      <c r="P27" s="99" t="s">
         <v>447</v>
       </c>
-      <c r="Q27" s="90"/>
-      <c r="S27" s="89" t="s">
+      <c r="Q27" s="100"/>
+      <c r="S27" s="99" t="s">
         <v>448</v>
       </c>
-      <c r="T27" s="90"/>
+      <c r="T27" s="100"/>
     </row>
     <row r="28" spans="1:192">
       <c r="B28" s="20" t="s">
@@ -19089,7 +19069,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F23C5D6-F53F-1347-9F05-D1DA7A03853D}">
-  <dimension ref="A1:Y89"/>
+  <dimension ref="A1:Y101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -21865,7 +21845,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
       <c r="J68">
-        <f t="shared" ref="J68:J99" si="15">K68-K67</f>
+        <f t="shared" ref="J68:J87" si="15">K68-K67</f>
         <v>0</v>
       </c>
       <c r="K68">
@@ -22686,9 +22666,109 @@
       </c>
     </row>
     <row r="89" spans="2:14">
-      <c r="E89" s="17">
+      <c r="E89" s="49">
         <f>E87/E3</f>
         <v>2.4905149051490514</v>
+      </c>
+      <c r="F89" s="49">
+        <f>F87/F3</f>
+        <v>1.4670340156553805</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14">
+      <c r="B94" s="1">
+        <v>43466</v>
+      </c>
+      <c r="C94">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="95" spans="2:14">
+      <c r="B95" s="1">
+        <v>43831</v>
+      </c>
+      <c r="C95">
+        <v>500</v>
+      </c>
+      <c r="D95" s="2">
+        <f>C95/C94-1</f>
+        <v>0.3550135501355014</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14">
+      <c r="B96" s="1">
+        <v>44197</v>
+      </c>
+      <c r="C96">
+        <v>524</v>
+      </c>
+      <c r="D96" s="2">
+        <f t="shared" ref="D96:D101" si="17">C96/C95-1</f>
+        <v>4.8000000000000043E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5">
+      <c r="B97" s="1">
+        <v>44562</v>
+      </c>
+      <c r="C97">
+        <v>720</v>
+      </c>
+      <c r="D97" s="2">
+        <f t="shared" si="17"/>
+        <v>0.37404580152671763</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5">
+      <c r="B98" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C98">
+        <v>732</v>
+      </c>
+      <c r="D98" s="2">
+        <f t="shared" si="17"/>
+        <v>1.6666666666666607E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5">
+      <c r="B99" s="1">
+        <v>45292</v>
+      </c>
+      <c r="C99">
+        <v>880</v>
+      </c>
+      <c r="D99" s="2">
+        <f t="shared" si="17"/>
+        <v>0.20218579234972678</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5">
+      <c r="B100" s="1">
+        <v>45658</v>
+      </c>
+      <c r="C100">
+        <v>732</v>
+      </c>
+      <c r="D100" s="2">
+        <f t="shared" si="17"/>
+        <v>-0.16818181818181821</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5">
+      <c r="B101" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C101">
+        <v>919</v>
+      </c>
+      <c r="D101" s="2">
+        <f t="shared" si="17"/>
+        <v>0.25546448087431695</v>
+      </c>
+      <c r="E101" s="2">
+        <f>AVERAGE(D95:D101)</f>
+        <v>0.15474206762444445</v>
       </c>
     </row>
   </sheetData>
@@ -23931,48 +24011,48 @@
     </row>
     <row r="2" spans="1:9" ht="14" thickBot="1"/>
     <row r="3" spans="1:9">
-      <c r="A3" s="109" t="s">
+      <c r="A3" s="82" t="s">
         <v>726</v>
       </c>
-      <c r="B3" s="109"/>
+      <c r="B3" s="82"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="106" t="s">
+      <c r="A4" t="s">
         <v>727</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4">
         <v>0.72855648647500826</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="B5" s="111">
+      <c r="B5" s="5">
         <v>0.5307945539848089</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="106" t="s">
+      <c r="A6" t="s">
         <v>729</v>
       </c>
-      <c r="B6" s="106">
+      <c r="B6">
         <v>0.52507253635047735</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="106" t="s">
+      <c r="A7" t="s">
         <v>730</v>
       </c>
-      <c r="B7" s="106">
+      <c r="B7">
         <v>137.91709030937318</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14" thickBot="1">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="80" t="s">
         <v>731</v>
       </c>
-      <c r="B8" s="107">
+      <c r="B8" s="80">
         <v>84</v>
       </c>
     </row>
@@ -23982,156 +24062,154 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="108"/>
-      <c r="B11" s="108" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="81" t="s">
         <v>737</v>
       </c>
-      <c r="C11" s="108" t="s">
+      <c r="C11" s="81" t="s">
         <v>738</v>
       </c>
-      <c r="D11" s="108" t="s">
+      <c r="D11" s="81" t="s">
         <v>739</v>
       </c>
-      <c r="E11" s="108" t="s">
+      <c r="E11" s="81" t="s">
         <v>740</v>
       </c>
-      <c r="F11" s="108" t="s">
+      <c r="F11" s="81" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="106" t="s">
+      <c r="A12" t="s">
         <v>733</v>
       </c>
-      <c r="B12" s="106">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="106">
+      <c r="C12">
         <v>1764466.5865441258</v>
       </c>
-      <c r="D12" s="106">
+      <c r="D12">
         <v>1764466.5865441258</v>
       </c>
-      <c r="E12" s="106">
+      <c r="E12">
         <v>92.763529912960863</v>
       </c>
-      <c r="F12" s="106">
+      <c r="F12">
         <v>4.0056399290842194E-15</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="106" t="s">
+      <c r="A13" t="s">
         <v>734</v>
       </c>
-      <c r="B13" s="106">
+      <c r="B13">
         <v>82</v>
       </c>
-      <c r="C13" s="106">
+      <c r="C13">
         <v>1559732.1515511111</v>
       </c>
-      <c r="D13" s="106">
+      <c r="D13">
         <v>19021.123799403795</v>
       </c>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
     </row>
     <row r="14" spans="1:9" ht="14" thickBot="1">
-      <c r="A14" s="107" t="s">
+      <c r="A14" s="80" t="s">
         <v>735</v>
       </c>
-      <c r="B14" s="107">
+      <c r="B14" s="80">
         <v>83</v>
       </c>
-      <c r="C14" s="107">
+      <c r="C14" s="80">
         <v>3324198.7380952369</v>
       </c>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
     </row>
     <row r="15" spans="1:9" ht="14" thickBot="1"/>
     <row r="16" spans="1:9">
-      <c r="A16" s="108"/>
-      <c r="B16" s="108" t="s">
+      <c r="A16" s="81"/>
+      <c r="B16" s="81" t="s">
         <v>742</v>
       </c>
-      <c r="C16" s="108" t="s">
+      <c r="C16" s="81" t="s">
         <v>730</v>
       </c>
-      <c r="D16" s="108" t="s">
+      <c r="D16" s="81" t="s">
         <v>743</v>
       </c>
-      <c r="E16" s="110" t="s">
+      <c r="E16" s="83" t="s">
         <v>744</v>
       </c>
-      <c r="F16" s="108" t="s">
+      <c r="F16" s="81" t="s">
         <v>745</v>
       </c>
-      <c r="G16" s="108" t="s">
+      <c r="G16" s="81" t="s">
         <v>746</v>
       </c>
-      <c r="H16" s="108" t="s">
+      <c r="H16" s="81" t="s">
         <v>747</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="81" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="106" t="s">
+      <c r="A17" t="s">
         <v>736</v>
       </c>
-      <c r="B17" s="106">
+      <c r="B17">
         <v>524.7238755364599</v>
       </c>
-      <c r="C17" s="106">
+      <c r="C17">
         <v>22.727031577421609</v>
       </c>
-      <c r="D17" s="106">
+      <c r="D17">
         <v>23.088095501999124</v>
       </c>
-      <c r="E17" s="111">
+      <c r="E17" s="5">
         <v>1.2437543878042374E-37</v>
       </c>
-      <c r="F17" s="106">
+      <c r="F17">
         <v>479.51256987086629</v>
       </c>
-      <c r="G17" s="106">
+      <c r="G17">
         <v>569.93518120205351</v>
       </c>
-      <c r="H17" s="106">
+      <c r="H17">
         <v>479.51256987086629</v>
       </c>
-      <c r="I17" s="106">
+      <c r="I17">
         <v>569.93518120205351</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="14" thickBot="1">
-      <c r="A18" s="107">
+      <c r="A18" s="80">
         <v>0.75</v>
       </c>
-      <c r="B18" s="107">
+      <c r="B18" s="80">
         <v>68.947683036964577</v>
       </c>
-      <c r="C18" s="107">
+      <c r="C18" s="80">
         <v>7.1586485788656766</v>
       </c>
-      <c r="D18" s="107">
+      <c r="D18" s="80">
         <v>9.6313825545951968</v>
       </c>
-      <c r="E18" s="112">
+      <c r="E18" s="84">
         <v>4.0056399290843922E-15</v>
       </c>
-      <c r="F18" s="107">
+      <c r="F18" s="80">
         <v>54.706850575007749</v>
       </c>
-      <c r="G18" s="107">
+      <c r="G18" s="80">
         <v>83.188515498921404</v>
       </c>
-      <c r="H18" s="107">
+      <c r="H18" s="80">
         <v>54.706850575007749</v>
       </c>
-      <c r="I18" s="107">
+      <c r="I18" s="80">
         <v>83.188515498921404</v>
       </c>
     </row>
@@ -24142,937 +24220,937 @@
     </row>
     <row r="23" spans="1:9" ht="14" thickBot="1"/>
     <row r="24" spans="1:9">
-      <c r="A24" s="108" t="s">
+      <c r="A24" s="81" t="s">
         <v>750</v>
       </c>
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="81" t="s">
         <v>788</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="81" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="106">
+      <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="106">
+      <c r="B25">
         <v>576.43463781418336</v>
       </c>
-      <c r="C25" s="106">
+      <c r="C25">
         <v>-199.43463781418336</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="106">
+      <c r="A26">
         <v>2</v>
       </c>
-      <c r="B26" s="106">
+      <c r="B26">
         <v>576.43463781418336</v>
       </c>
-      <c r="C26" s="106">
+      <c r="C26">
         <v>-174.43463781418336</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="106">
+      <c r="A27">
         <v>3</v>
       </c>
-      <c r="B27" s="106">
+      <c r="B27">
         <v>576.43463781418336</v>
       </c>
-      <c r="C27" s="106">
+      <c r="C27">
         <v>-185.93463781418336</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="106">
+      <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="106">
+      <c r="B28">
         <v>576.43463781418336</v>
       </c>
-      <c r="C28" s="106">
+      <c r="C28">
         <v>-146.43463781418336</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="106">
+      <c r="A29">
         <v>5</v>
       </c>
-      <c r="B29" s="106">
+      <c r="B29">
         <v>576.43463781418336</v>
       </c>
-      <c r="C29" s="106">
+      <c r="C29">
         <v>-161.43463781418336</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="106">
+      <c r="A30">
         <v>6</v>
       </c>
-      <c r="B30" s="106">
+      <c r="B30">
         <v>576.43463781418336</v>
       </c>
-      <c r="C30" s="106">
+      <c r="C30">
         <v>-176.43463781418336</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="106">
+      <c r="A31">
         <v>7</v>
       </c>
-      <c r="B31" s="106">
+      <c r="B31">
         <v>576.43463781418336</v>
       </c>
-      <c r="C31" s="106">
+      <c r="C31">
         <v>-189.93463781418336</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="106">
+      <c r="A32">
         <v>8</v>
       </c>
-      <c r="B32" s="106">
+      <c r="B32">
         <v>576.43463781418336</v>
       </c>
-      <c r="C32" s="106">
+      <c r="C32">
         <v>-191.43463781418336</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="106">
+      <c r="A33">
         <v>9</v>
       </c>
-      <c r="B33" s="106">
+      <c r="B33">
         <v>576.43463781418336</v>
       </c>
-      <c r="C33" s="106">
+      <c r="C33">
         <v>-193.43463781418336</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="106">
+      <c r="A34">
         <v>10</v>
       </c>
-      <c r="B34" s="106">
+      <c r="B34">
         <v>576.43463781418336</v>
       </c>
-      <c r="C34" s="106">
+      <c r="C34">
         <v>-186.43463781418336</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="106">
+      <c r="A35">
         <v>11</v>
       </c>
-      <c r="B35" s="106">
+      <c r="B35">
         <v>576.43463781418336</v>
       </c>
-      <c r="C35" s="106">
+      <c r="C35">
         <v>-30.434637814183361</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="106">
+      <c r="A36">
         <v>12</v>
       </c>
-      <c r="B36" s="106">
+      <c r="B36">
         <v>576.43463781418336</v>
       </c>
-      <c r="C36" s="106">
+      <c r="C36">
         <v>-76.434637814183361</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="106">
+      <c r="A37">
         <v>13</v>
       </c>
-      <c r="B37" s="106">
+      <c r="B37">
         <v>576.43463781418336</v>
       </c>
-      <c r="C37" s="106">
+      <c r="C37">
         <v>-82.434637814183361</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="106">
+      <c r="A38">
         <v>14</v>
       </c>
-      <c r="B38" s="106">
+      <c r="B38">
         <v>576.43463781418336</v>
       </c>
-      <c r="C38" s="106">
+      <c r="C38">
         <v>-200.43463781418336</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="106">
+      <c r="A39">
         <v>15</v>
       </c>
-      <c r="B39" s="106">
+      <c r="B39">
         <v>531.61864384015632</v>
       </c>
-      <c r="C39" s="106">
+      <c r="C39">
         <v>-79.618643840156324</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="106">
+      <c r="A40">
         <v>16</v>
       </c>
-      <c r="B40" s="106">
+      <c r="B40">
         <v>531.61864384015632</v>
       </c>
-      <c r="C40" s="106">
+      <c r="C40">
         <v>-68.618643840156324</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="106">
+      <c r="A41">
         <v>17</v>
       </c>
-      <c r="B41" s="106">
+      <c r="B41">
         <v>531.61864384015632</v>
       </c>
-      <c r="C41" s="106">
+      <c r="C41">
         <v>-88.618643840156324</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="106">
+      <c r="A42">
         <v>18</v>
       </c>
-      <c r="B42" s="106">
+      <c r="B42">
         <v>531.61864384015632</v>
       </c>
-      <c r="C42" s="106">
+      <c r="C42">
         <v>-95.618643840156324</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="106">
+      <c r="A43">
         <v>19</v>
       </c>
-      <c r="B43" s="106">
+      <c r="B43">
         <v>531.61864384015632</v>
       </c>
-      <c r="C43" s="106">
+      <c r="C43">
         <v>-108.61864384015632</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="106">
+      <c r="A44">
         <v>20</v>
       </c>
-      <c r="B44" s="106">
+      <c r="B44">
         <v>531.61864384015632</v>
       </c>
-      <c r="C44" s="106">
+      <c r="C44">
         <v>-76.618643840156324</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="106">
+      <c r="A45">
         <v>21</v>
       </c>
-      <c r="B45" s="106">
+      <c r="B45">
         <v>531.61864384015632</v>
       </c>
-      <c r="C45" s="106">
+      <c r="C45">
         <v>-96.618643840156324</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="106">
+      <c r="A46">
         <v>22</v>
       </c>
-      <c r="B46" s="106">
+      <c r="B46">
         <v>531.61864384015632</v>
       </c>
-      <c r="C46" s="106">
+      <c r="C46">
         <v>-36.618643840156324</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="106">
+      <c r="A47">
         <v>23</v>
       </c>
-      <c r="B47" s="106">
+      <c r="B47">
         <v>531.61864384015632</v>
       </c>
-      <c r="C47" s="106">
+      <c r="C47">
         <v>28.381356159843676</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="106">
+      <c r="A48">
         <v>24</v>
       </c>
-      <c r="B48" s="106">
+      <c r="B48">
         <v>531.61864384015632</v>
       </c>
-      <c r="C48" s="106">
+      <c r="C48">
         <v>-7.6186438401563237</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="106">
+      <c r="A49">
         <v>25</v>
       </c>
-      <c r="B49" s="106">
+      <c r="B49">
         <v>531.61864384015632</v>
       </c>
-      <c r="C49" s="106">
+      <c r="C49">
         <v>-29.618643840156324</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="106">
+      <c r="A50">
         <v>26</v>
       </c>
-      <c r="B50" s="106">
+      <c r="B50">
         <v>531.61864384015632</v>
       </c>
-      <c r="C50" s="106">
+      <c r="C50">
         <v>32.381356159843676</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="106">
+      <c r="A51">
         <v>27</v>
       </c>
-      <c r="B51" s="106">
+      <c r="B51">
         <v>531.61864384015632</v>
       </c>
-      <c r="C51" s="106">
+      <c r="C51">
         <v>93.381356159843676</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="106">
+      <c r="A52">
         <v>28</v>
       </c>
-      <c r="B52" s="106">
+      <c r="B52">
         <v>531.61864384015632</v>
       </c>
-      <c r="C52" s="106">
+      <c r="C52">
         <v>104.38135615984368</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="106">
+      <c r="A53">
         <v>29</v>
       </c>
-      <c r="B53" s="106">
+      <c r="B53">
         <v>531.61864384015632</v>
       </c>
-      <c r="C53" s="106">
+      <c r="C53">
         <v>143.38135615984368</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="106">
+      <c r="A54">
         <v>30</v>
       </c>
-      <c r="B54" s="106">
+      <c r="B54">
         <v>531.61864384015632</v>
       </c>
-      <c r="C54" s="106">
+      <c r="C54">
         <v>214.38135615984368</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="106">
+      <c r="A55">
         <v>31</v>
       </c>
-      <c r="B55" s="106">
+      <c r="B55">
         <v>531.61864384015632</v>
       </c>
-      <c r="C55" s="106">
+      <c r="C55">
         <v>235.38135615984368</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="106">
+      <c r="A56">
         <v>32</v>
       </c>
-      <c r="B56" s="106">
+      <c r="B56">
         <v>531.61864384015632</v>
       </c>
-      <c r="C56" s="106">
+      <c r="C56">
         <v>258.38135615984368</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="106">
+      <c r="A57">
         <v>33</v>
       </c>
-      <c r="B57" s="106">
+      <c r="B57">
         <v>531.61864384015632</v>
       </c>
-      <c r="C57" s="106">
+      <c r="C57">
         <v>231.38135615984368</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="106">
+      <c r="A58">
         <v>34</v>
       </c>
-      <c r="B58" s="106">
+      <c r="B58">
         <v>531.61864384015632</v>
       </c>
-      <c r="C58" s="106">
+      <c r="C58">
         <v>271.38135615984368</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="106">
+      <c r="A59">
         <v>35</v>
       </c>
-      <c r="B59" s="106">
+      <c r="B59">
         <v>531.61864384015632</v>
       </c>
-      <c r="C59" s="106">
+      <c r="C59">
         <v>303.38135615984368</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="106">
+      <c r="A60">
         <v>36</v>
       </c>
-      <c r="B60" s="106">
+      <c r="B60">
         <v>541.96079629570102</v>
       </c>
-      <c r="C60" s="106">
+      <c r="C60">
         <v>178.03920370429898</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="106">
+      <c r="A61">
         <v>37</v>
       </c>
-      <c r="B61" s="106">
+      <c r="B61">
         <v>541.96079629570102</v>
       </c>
-      <c r="C61" s="106">
+      <c r="C61">
         <v>138.03920370429898</v>
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="106">
+      <c r="A62">
         <v>38</v>
       </c>
-      <c r="B62" s="106">
+      <c r="B62">
         <v>559.19771705494213</v>
       </c>
-      <c r="C62" s="106">
+      <c r="C62">
         <v>124.80228294505787</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="106">
+      <c r="A63">
         <v>39</v>
       </c>
-      <c r="B63" s="106">
+      <c r="B63">
         <v>576.43463781418336</v>
       </c>
-      <c r="C63" s="106">
+      <c r="C63">
         <v>122.56536218581664</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="106">
+      <c r="A64">
         <v>40</v>
       </c>
-      <c r="B64" s="106">
+      <c r="B64">
         <v>576.43463781418336</v>
       </c>
-      <c r="C64" s="106">
+      <c r="C64">
         <v>115.56536218581664</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="106">
+      <c r="A65">
         <v>41</v>
       </c>
-      <c r="B65" s="106">
+      <c r="B65">
         <v>593.67155857342448</v>
       </c>
-      <c r="C65" s="106">
+      <c r="C65">
         <v>46.328441426575523</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="106">
+      <c r="A66">
         <v>42</v>
       </c>
-      <c r="B66" s="106">
+      <c r="B66">
         <v>610.90847933266559</v>
       </c>
-      <c r="C66" s="106">
+      <c r="C66">
         <v>130.09152066733441</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="106">
+      <c r="A67">
         <v>43</v>
       </c>
-      <c r="B67" s="106">
+      <c r="B67">
         <v>610.90847933266559</v>
       </c>
-      <c r="C67" s="106">
+      <c r="C67">
         <v>32.091520667334407</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="106">
+      <c r="A68">
         <v>44</v>
       </c>
-      <c r="B68" s="106">
+      <c r="B68">
         <v>645.38232085114794</v>
       </c>
-      <c r="C68" s="106">
+      <c r="C68">
         <v>-75.382320851147938</v>
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="106">
+      <c r="A69">
         <v>45</v>
       </c>
-      <c r="B69" s="106">
+      <c r="B69">
         <v>679.85616236963017</v>
       </c>
-      <c r="C69" s="106">
+      <c r="C69">
         <v>-65.856162369630169</v>
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="106">
+      <c r="A70">
         <v>46</v>
       </c>
-      <c r="B70" s="106">
+      <c r="B70">
         <v>679.85616236963017</v>
       </c>
-      <c r="C70" s="106">
+      <c r="C70">
         <v>3.1438376303698305</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="106">
+      <c r="A71">
         <v>47</v>
       </c>
-      <c r="B71" s="106">
+      <c r="B71">
         <v>731.56692464735363</v>
       </c>
-      <c r="C71" s="106">
+      <c r="C71">
         <v>0.43307535264636954</v>
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="106">
+      <c r="A72">
         <v>48</v>
       </c>
-      <c r="B72" s="106">
+      <c r="B72">
         <v>766.04076616583598</v>
       </c>
-      <c r="C72" s="106">
+      <c r="C72">
         <v>-34.040766165835976</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="106">
+      <c r="A73">
         <v>49</v>
       </c>
-      <c r="B73" s="106">
+      <c r="B73">
         <v>766.04076616583598</v>
       </c>
-      <c r="C73" s="106">
+      <c r="C73">
         <v>-53.040766165835976</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="106">
+      <c r="A74">
         <v>50</v>
       </c>
-      <c r="B74" s="106">
+      <c r="B74">
         <v>800.51460768431821</v>
       </c>
-      <c r="C74" s="106">
+      <c r="C74">
         <v>-124.51460768431821</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="106">
+      <c r="A75">
         <v>51</v>
       </c>
-      <c r="B75" s="106">
+      <c r="B75">
         <v>817.75152844355932</v>
       </c>
-      <c r="C75" s="106">
+      <c r="C75">
         <v>-90.751528443559323</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="106">
+      <c r="A76">
         <v>52</v>
       </c>
-      <c r="B76" s="106">
+      <c r="B76">
         <v>817.75152844355932</v>
       </c>
-      <c r="C76" s="106">
+      <c r="C76">
         <v>-102.75152844355932</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="106">
+      <c r="A77">
         <v>53</v>
       </c>
-      <c r="B77" s="106">
+      <c r="B77">
         <v>834.98844920280044</v>
       </c>
-      <c r="C77" s="106">
+      <c r="C77">
         <v>-90.988449202800439</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="106">
+      <c r="A78">
         <v>54</v>
       </c>
-      <c r="B78" s="106">
+      <c r="B78">
         <v>869.46229072128278</v>
       </c>
-      <c r="C78" s="106">
+      <c r="C78">
         <v>-139.46229072128278</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="106">
+      <c r="A79">
         <v>55</v>
       </c>
-      <c r="B79" s="106">
+      <c r="B79">
         <v>869.46229072128278</v>
       </c>
-      <c r="C79" s="106">
+      <c r="C79">
         <v>-151.46229072128278</v>
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="106">
+      <c r="A80">
         <v>56</v>
       </c>
-      <c r="B80" s="106">
+      <c r="B80">
         <v>886.6992114805239</v>
       </c>
-      <c r="C80" s="106">
+      <c r="C80">
         <v>-173.6992114805239</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="106">
+      <c r="A81">
         <v>57</v>
       </c>
-      <c r="B81" s="106">
+      <c r="B81">
         <v>886.6992114805239</v>
       </c>
-      <c r="C81" s="106">
+      <c r="C81">
         <v>-169.6992114805239</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="106">
+      <c r="A82">
         <v>58</v>
       </c>
-      <c r="B82" s="106">
+      <c r="B82">
         <v>886.6992114805239</v>
       </c>
-      <c r="C82" s="106">
+      <c r="C82">
         <v>-44.6992114805239</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="106">
+      <c r="A83">
         <v>59</v>
       </c>
-      <c r="B83" s="106">
+      <c r="B83">
         <v>886.6992114805239</v>
       </c>
-      <c r="C83" s="106">
+      <c r="C83">
         <v>-27.6992114805239</v>
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="106">
+      <c r="A84">
         <v>60</v>
       </c>
-      <c r="B84" s="106">
+      <c r="B84">
         <v>886.6992114805239</v>
       </c>
-      <c r="C84" s="106">
+      <c r="C84">
         <v>-6.6992114805238998</v>
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="106">
+      <c r="A85">
         <v>61</v>
       </c>
-      <c r="B85" s="106">
+      <c r="B85">
         <v>886.6992114805239</v>
       </c>
-      <c r="C85" s="106">
+      <c r="C85">
         <v>-11.6992114805239</v>
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="106">
+      <c r="A86">
         <v>62</v>
       </c>
-      <c r="B86" s="106">
+      <c r="B86">
         <v>886.6992114805239</v>
       </c>
-      <c r="C86" s="106">
+      <c r="C86">
         <v>37.3007885194761</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="106">
+      <c r="A87">
         <v>63</v>
       </c>
-      <c r="B87" s="106">
+      <c r="B87">
         <v>886.6992114805239</v>
       </c>
-      <c r="C87" s="106">
+      <c r="C87">
         <v>58.3007885194761</v>
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="106">
+      <c r="A88">
         <v>64</v>
       </c>
-      <c r="B88" s="106">
+      <c r="B88">
         <v>886.6992114805239</v>
       </c>
-      <c r="C88" s="106">
+      <c r="C88">
         <v>181.3007885194761</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="106">
+      <c r="A89">
         <v>65</v>
       </c>
-      <c r="B89" s="106">
+      <c r="B89">
         <v>886.6992114805239</v>
       </c>
-      <c r="C89" s="106">
+      <c r="C89">
         <v>175.3007885194761</v>
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="106">
+      <c r="A90">
         <v>66</v>
       </c>
-      <c r="B90" s="106">
+      <c r="B90">
         <v>886.6992114805239</v>
       </c>
-      <c r="C90" s="106">
+      <c r="C90">
         <v>199.3007885194761</v>
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="106">
+      <c r="A91">
         <v>67</v>
       </c>
-      <c r="B91" s="106">
+      <c r="B91">
         <v>869.46229072128278</v>
       </c>
-      <c r="C91" s="106">
+      <c r="C91">
         <v>202.53770927871722</v>
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="106">
+      <c r="A92">
         <v>68</v>
       </c>
-      <c r="B92" s="106">
+      <c r="B92">
         <v>869.46229072128278</v>
       </c>
-      <c r="C92" s="106">
+      <c r="C92">
         <v>182.53770927871722</v>
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="106">
+      <c r="A93">
         <v>69</v>
       </c>
-      <c r="B93" s="106">
+      <c r="B93">
         <v>869.46229072128278</v>
       </c>
-      <c r="C93" s="106">
+      <c r="C93">
         <v>224.53770927871722</v>
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="106">
+      <c r="A94">
         <v>70</v>
       </c>
-      <c r="B94" s="106">
+      <c r="B94">
         <v>869.46229072128278</v>
       </c>
-      <c r="C94" s="106">
+      <c r="C94">
         <v>170.53770927871722</v>
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="106">
+      <c r="A95">
         <v>71</v>
       </c>
-      <c r="B95" s="106">
+      <c r="B95">
         <v>852.22536996204167</v>
       </c>
-      <c r="C95" s="106">
+      <c r="C95">
         <v>52.774630037958332</v>
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="106">
+      <c r="A96">
         <v>72</v>
       </c>
-      <c r="B96" s="106">
+      <c r="B96">
         <v>852.22536996204167</v>
       </c>
-      <c r="C96" s="106">
+      <c r="C96">
         <v>-120.22536996204167</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="106">
+      <c r="A97">
         <v>73</v>
       </c>
-      <c r="B97" s="106">
+      <c r="B97">
         <v>852.22536996204167</v>
       </c>
-      <c r="C97" s="106">
+      <c r="C97">
         <v>-193.22536996204167</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="106">
+      <c r="A98">
         <v>74</v>
       </c>
-      <c r="B98" s="106">
+      <c r="B98">
         <v>834.98844920280044</v>
       </c>
-      <c r="C98" s="106">
+      <c r="C98">
         <v>-172.98844920280044</v>
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="106">
+      <c r="A99">
         <v>75</v>
       </c>
-      <c r="B99" s="106">
+      <c r="B99">
         <v>834.98844920280044</v>
       </c>
-      <c r="C99" s="106">
+      <c r="C99">
         <v>-79.988449202800439</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="106">
+      <c r="A100">
         <v>76</v>
       </c>
-      <c r="B100" s="106">
+      <c r="B100">
         <v>834.98844920280044</v>
       </c>
-      <c r="C100" s="106">
+      <c r="C100">
         <v>-14.988449202800439</v>
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="106">
+      <c r="A101">
         <v>77</v>
       </c>
-      <c r="B101" s="106">
+      <c r="B101">
         <v>817.75152844355932</v>
       </c>
-      <c r="C101" s="106">
+      <c r="C101">
         <v>32.248471556440677</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="106">
+      <c r="A102">
         <v>78</v>
       </c>
-      <c r="B102" s="106">
+      <c r="B102">
         <v>817.75152844355932</v>
       </c>
-      <c r="C102" s="106">
+      <c r="C102">
         <v>25.248471556440677</v>
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="106">
+      <c r="A103">
         <v>79</v>
       </c>
-      <c r="B103" s="106">
+      <c r="B103">
         <v>817.75152844355932</v>
       </c>
-      <c r="C103" s="106">
+      <c r="C103">
         <v>-16.751528443559323</v>
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="106">
+      <c r="A104">
         <v>80</v>
       </c>
-      <c r="B104" s="106">
+      <c r="B104">
         <v>800.51460768431821</v>
       </c>
-      <c r="C104" s="106">
+      <c r="C104">
         <v>9.4853923156817928</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="106">
+      <c r="A105">
         <v>81</v>
       </c>
-      <c r="B105" s="106">
+      <c r="B105">
         <v>800.51460768431821</v>
       </c>
-      <c r="C105" s="106">
+      <c r="C105">
         <v>125.48539231568179</v>
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="106">
+      <c r="A106">
         <v>82</v>
       </c>
-      <c r="B106" s="106">
+      <c r="B106">
         <v>800.51460768431821</v>
       </c>
-      <c r="C106" s="106">
+      <c r="C106">
         <v>133.48539231568179</v>
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="106">
+      <c r="A107">
         <v>83</v>
       </c>
-      <c r="B107" s="106">
+      <c r="B107">
         <v>800.51460768431821</v>
       </c>
-      <c r="C107" s="106">
+      <c r="C107">
         <v>90.485392315681793</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="14" thickBot="1">
-      <c r="A108" s="107">
+      <c r="A108" s="80">
         <v>84</v>
       </c>
-      <c r="B108" s="107">
+      <c r="B108" s="80">
         <v>783.27768692507709</v>
       </c>
-      <c r="C108" s="107">
+      <c r="C108" s="80">
         <v>135.72231307492291</v>
       </c>
     </row>
@@ -25100,24 +25178,24 @@
     </row>
     <row r="2" spans="1:33" s="5" customFormat="1">
       <c r="A2" s="67"/>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="95" t="s">
         <v>345</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="J2" s="91" t="s">
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="J2" s="95" t="s">
         <v>340</v>
       </c>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
     </row>
     <row r="3" spans="1:33" s="5" customFormat="1">
       <c r="B3" s="5" t="s">
@@ -25165,7 +25243,7 @@
       <c r="R3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="S3" s="113">
+      <c r="S3" s="92">
         <f>AVERAGE(C4:C88)</f>
         <v>685</v>
       </c>
@@ -25179,7 +25257,7 @@
       <c r="X3" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="Y3" s="100">
+      <c r="Y3" s="89">
         <f>MIN(H4:H88)</f>
         <v>-0.2389</v>
       </c>
@@ -25231,7 +25309,7 @@
       <c r="R4" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="S4" s="114">
+      <c r="S4" s="93">
         <f>MEDIAN(C4:C88)</f>
         <v>713</v>
       </c>
@@ -25297,7 +25375,7 @@
       <c r="R5" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="S5" s="115">
+      <c r="S5" s="94">
         <f>MODE(C4:C88)</f>
         <v>732</v>
       </c>
@@ -25466,7 +25544,7 @@
       <c r="P8" s="2">
         <v>1.78E-2</v>
       </c>
-      <c r="R8" s="104" t="s">
+      <c r="R8" s="14" t="s">
         <v>782</v>
       </c>
       <c r="S8" s="16">
@@ -25518,8 +25596,7 @@
       <c r="P9" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="R9" s="103"/>
-      <c r="S9" s="102"/>
+      <c r="S9" s="2"/>
       <c r="U9" s="11" t="s">
         <v>774</v>
       </c>
@@ -25742,7 +25819,7 @@
       <c r="R13" s="50" t="s">
         <v>786</v>
       </c>
-      <c r="S13" s="99">
+      <c r="S13" s="88">
         <f>(1+S7)^12-1</f>
         <v>0.2038425120002183</v>
       </c>
@@ -25791,10 +25868,10 @@
       <c r="P14" s="2">
         <v>-2.58E-2</v>
       </c>
-      <c r="R14" s="97" t="s">
+      <c r="R14" s="86" t="s">
         <v>787</v>
       </c>
-      <c r="S14" s="105">
+      <c r="S14" s="91">
         <f>(1+S8)^12-1</f>
         <v>6.9158775797845795E-2</v>
       </c>
@@ -25843,10 +25920,10 @@
       <c r="P15" s="2">
         <v>1.5699999999999999E-2</v>
       </c>
-      <c r="R15" s="98" t="s">
+      <c r="R15" s="87" t="s">
         <v>776</v>
       </c>
-      <c r="S15" s="101">
+      <c r="S15" s="90">
         <f>V6/V9</f>
         <v>2.4768854754666045</v>
       </c>
@@ -29220,11 +29297,11 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="101" t="s">
         <v>450</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="94"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="103"/>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="70" t="s">
@@ -30114,10 +30191,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="104" t="s">
         <v>458</v>
       </c>
-      <c r="C2" s="96"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="1:3" ht="15">
       <c r="B3" s="79" t="s">
